--- a/qc/ADAM-PROGRAMMING-TRACKER.xlsx
+++ b/qc/ADAM-PROGRAMMING-TRACKER.xlsx
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q7" s="18" t="inlineStr">
         <is>
-          <t/>
+          <t>AL-04: PARAMCD='PFSINV' not derived because the synthetic data has no separate BICR vs Investigator assessment. Affects T-EFF-11. Accepted — not a defect.</t>
         </is>
       </c>
       <c r="R7" s="18" t="inlineStr">

--- a/qc/ADAM-PROGRAMMING-TRACKER.xlsx
+++ b/qc/ADAM-PROGRAMMING-TRACKER.xlsx
@@ -520,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
@@ -695,7 +695,7 @@
       </c>
       <c r="K2" s="16" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="L2" s="16" t="inlineStr">
@@ -747,46 +747,46 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>ADLB</t>
+          <t>ADCM</t>
         </is>
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>Basic Data Structure</t>
+          <t>Occurrence Data Structure</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>LB + ADSL</t>
+          <t>CM + SUPPCM + ADSL</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>programs/adam/adlb.R</t>
+          <t>programs/adam/adcm.R</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>ADAM-MAPPING-SPEC.md §3</t>
+          <t>ADAM-MAPPING-SPEC.md §10</t>
         </is>
       </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>T-LB-01/02, L-LB-01</t>
+          <t>T-CM-01</t>
         </is>
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
-          <t>datasets/adam/adlb.parquet</t>
+          <t>datasets/adam/adcm.parquet</t>
         </is>
       </c>
       <c r="H3" s="17" t="inlineStr">
         <is>
-          <t>122,601</t>
+          <t>2,197</t>
         </is>
       </c>
       <c r="I3" s="17">
-        <v>1487.8</v>
+        <v>67.1</v>
       </c>
       <c r="J3" s="17" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       </c>
       <c r="K3" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="L3" s="17" t="inlineStr">
@@ -847,46 +847,46 @@
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>ADRS</t>
+          <t>ADDS</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>Basic Data Structure</t>
+          <t>Occurrence Data Structure</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>RS + ADSL + ADTR</t>
+          <t>DS + ADSL</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>programs/adam/adrs.R</t>
+          <t>programs/adam/adds.R</t>
         </is>
       </c>
       <c r="E4" s="17" t="inlineStr">
         <is>
-          <t>ADAM-MAPPING-SPEC.md §5</t>
+          <t>ADAM-MAPPING-SPEC.md §7</t>
         </is>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>T-EFF-05 (ORR), T-EFF-06 (DCR), T-EFF-13 (ORR-ITT)</t>
+          <t>T-DS-01</t>
         </is>
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>datasets/adam/adrs.parquet</t>
+          <t>datasets/adam/adds.parquet</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>3,662</t>
+          <t>1,350</t>
         </is>
       </c>
       <c r="I4" s="17">
-        <v>39.9</v>
+        <v>35.3</v>
       </c>
       <c r="J4" s="17" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
       </c>
       <c r="K4" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="L4" s="17" t="inlineStr">
@@ -947,46 +947,46 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>ADSL</t>
+          <t>ADDV</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>Subject-Level Analysis Dataset</t>
+          <t>Occurrence Data Structure</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>DM + SUPPDM + EX + DS + DD</t>
+          <t>ADSL.PPROTFL (DV not simulated)</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>programs/adam/adsl.R</t>
+          <t>programs/adam/addv.R</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>ADAM-MAPPING-SPEC.md §1</t>
+          <t>ADAM-MAPPING-SPEC.md §8</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>All — anchor</t>
+          <t>T-DS-02, T-DV-01, L-DS-01</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t>datasets/adam/adsl.parquet</t>
+          <t>datasets/adam/addv.parquet</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" s="17">
-        <v>37</v>
+        <v>9.7</v>
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="K5" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="L5" s="17" t="inlineStr">
@@ -1047,241 +1047,841 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
+          <t>ADEX</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Basic Data Structure</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>EX + ADSL</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>programs/adam/adex.R</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>ADAM-MAPPING-SPEC.md §9</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>T-EX-01 (DOSEAMT/CUMDOSE/RDI)</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>datasets/adam/adex.parquet</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>16,097</t>
+        </is>
+      </c>
+      <c r="I6" s="17">
+        <v>116.5</v>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="L6" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" s="17" t="inlineStr">
+        <is>
+          <t>Independent double programming</t>
+        </is>
+      </c>
+      <c r="N6" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" s="17" t="inlineStr">
+        <is>
+          <t>Programmed — pending QC</t>
+        </is>
+      </c>
+      <c r="Q6" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>ADLB</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Basic Data Structure</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>LB + ADSL</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>programs/adam/adlb.R</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>ADAM-MAPPING-SPEC.md §3</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>T-LB-01/02, L-LB-01</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>datasets/adam/adlb.parquet</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>122,601</t>
+        </is>
+      </c>
+      <c r="I7" s="17">
+        <v>1487.8</v>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="L7" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" s="17" t="inlineStr">
+        <is>
+          <t>Independent double programming</t>
+        </is>
+      </c>
+      <c r="N7" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" s="17" t="inlineStr">
+        <is>
+          <t>Programmed — pending QC</t>
+        </is>
+      </c>
+      <c r="Q7" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>ADMH</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Occurrence Data Structure</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>MH + ADSL</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>programs/adam/admh.R</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>ADAM-MAPPING-SPEC.md §12</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>T-MH-01</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>datasets/adam/admh.parquet</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>2,061</t>
+        </is>
+      </c>
+      <c r="I8" s="17">
+        <v>41.6</v>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" s="17" t="inlineStr">
+        <is>
+          <t>Independent double programming</t>
+        </is>
+      </c>
+      <c r="N8" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" s="17" t="inlineStr">
+        <is>
+          <t>Programmed — pending QC</t>
+        </is>
+      </c>
+      <c r="Q8" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>ADRS</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Basic Data Structure</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>RS + ADSL + ADTR</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>programs/adam/adrs.R</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>ADAM-MAPPING-SPEC.md §5</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>T-EFF-05 (ORR), T-EFF-06 (DCR), T-EFF-13 (ORR-ITT)</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>datasets/adam/adrs.parquet</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>3,662</t>
+        </is>
+      </c>
+      <c r="I9" s="17">
+        <v>39.9</v>
+      </c>
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" s="17" t="inlineStr">
+        <is>
+          <t>Independent double programming</t>
+        </is>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" s="17" t="inlineStr">
+        <is>
+          <t>Programmed — pending QC</t>
+        </is>
+      </c>
+      <c r="Q9" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Subject-Level Analysis Dataset</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>DM + SUPPDM + EX + DS + DD</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>programs/adam/adsl.R</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>ADAM-MAPPING-SPEC.md §1</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>All — anchor</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>datasets/adam/adsl.parquet</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="I10" s="17">
+        <v>37</v>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" s="17" t="inlineStr">
+        <is>
+          <t>Independent double programming</t>
+        </is>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" s="17" t="inlineStr">
+        <is>
+          <t>Programmed — pending QC</t>
+        </is>
+      </c>
+      <c r="Q10" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
           <t>ADTR</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Basic Data Structure</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>TR + ADSL</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>programs/adam/adtr.R</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>ADAM-MAPPING-SPEC.md §4</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>F-EFF-03 (Waterfall), F-EFF-04 (Spider)</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>datasets/adam/adtr.parquet</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>9,378</t>
         </is>
       </c>
-      <c r="I6" s="17">
+      <c r="I11" s="17">
         <v>165.5</v>
       </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K6" s="17" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" s="17" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" s="17" t="inlineStr">
         <is>
           <t>Independent double programming</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="N11" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" s="17" t="inlineStr">
         <is>
           <t>Programmed — pending QC</t>
         </is>
       </c>
-      <c r="Q6" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R6" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S6" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T6" s="20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="Q11" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R11" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S11" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T11" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>ADTTE</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Basic Data Structure</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>ADSL + ADRS + DS + DD</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>programs/adam/adtte.R</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>ADAM-MAPPING-SPEC.md §6</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>T-EFF-01..04, T-EFF-07..12, F-EFF-01/02/05/06</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>datasets/adam/adtte.parquet</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>1,918</t>
         </is>
       </c>
-      <c r="I7" s="18">
+      <c r="I12" s="17">
         <v>30</v>
       </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K7" s="18" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="L7" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M7" s="18" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" s="17" t="inlineStr">
         <is>
           <t>Independent double programming</t>
         </is>
       </c>
-      <c r="N7" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O7" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P7" s="18" t="inlineStr">
+      <c r="N12" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" s="17" t="inlineStr">
         <is>
           <t>Programmed — pending QC</t>
         </is>
       </c>
-      <c r="Q7" s="18" t="inlineStr">
+      <c r="Q12" s="17" t="inlineStr">
         <is>
           <t>AL-04: PARAMCD='PFSINV' not derived because the synthetic data has no separate BICR vs Investigator assessment. Affects T-EFF-11. Accepted — not a defect.</t>
         </is>
       </c>
-      <c r="R7" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S7" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T7" s="21" t="inlineStr">
+      <c r="R12" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S12" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T12" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>ADVS</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Basic Data Structure</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>VS + ADSL</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>programs/adam/advs.R</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>ADAM-MAPPING-SPEC.md §11</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>T-VS-01, T-VS-02</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>datasets/adam/advs.parquet</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>52,864</t>
+        </is>
+      </c>
+      <c r="I13" s="18">
+        <v>516.8</v>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" s="18" t="inlineStr">
+        <is>
+          <t>Independent double programming</t>
+        </is>
+      </c>
+      <c r="N13" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" s="18" t="inlineStr">
+        <is>
+          <t>Programmed — pending QC</t>
+        </is>
+      </c>
+      <c r="Q13" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R13" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S13" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T13" s="21" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="P2:P7">
+  <conditionalFormatting sqref="P2:P13">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Not started">
       <formula>NOT(ISERROR(SEARCH("Not started", P2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P7">
+  <conditionalFormatting sqref="P2:P13">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Programmed — pending QC">
       <formula>NOT(ISERROR(SEARCH("Programmed — pending QC", P2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P7">
+  <conditionalFormatting sqref="P2:P13">
     <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="QC in progress">
       <formula>NOT(ISERROR(SEARCH("QC in progress", P2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P7">
+  <conditionalFormatting sqref="P2:P13">
     <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="QC passed — issues none">
       <formula>NOT(ISERROR(SEARCH("QC passed — issues none", P2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P7">
+  <conditionalFormatting sqref="P2:P13">
     <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="QC passed — minor issues resolved">
       <formula>NOT(ISERROR(SEARCH("QC passed — minor issues resolved", P2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P7">
+  <conditionalFormatting sqref="P2:P13">
     <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="QC failed — under rework">
       <formula>NOT(ISERROR(SEARCH("QC failed — under rework", P2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P7">
+  <conditionalFormatting sqref="P2:P13">
     <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="Locked">
       <formula>NOT(ISERROR(SEARCH("Locked", P2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="0" sqref="P2:P7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="0" sqref="P2:P13">
       <formula1>"Not started,Programmed — pending QC,QC in progress,QC passed — issues none,QC passed — minor issues resolved,QC failed — under rework,Locked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1463,7 +2063,7 @@
     <row r="2">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Generated 2026-05-16 — synthetic data, not for regulatory submission</t>
+          <t>Generated 2026-05-17 — synthetic data, not for regulatory submission</t>
         </is>
       </c>
       <c r="B2" s="16"/>

--- a/qc/ADAM-PROGRAMMING-TRACKER.xlsx
+++ b/qc/ADAM-PROGRAMMING-TRACKER.xlsx
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="I4" s="17">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="J4" s="17" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>ADSL.PPROTFL (DV not simulated)</t>
+          <t>DV + ADSL</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
@@ -982,11 +982,11 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>337</t>
         </is>
       </c>
       <c r="I5" s="17">
-        <v>9.7</v>
+        <v>25.1</v>
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>

--- a/qc/ADAM-PROGRAMMING-TRACKER.xlsx
+++ b/qc/ADAM-PROGRAMMING-TRACKER.xlsx
@@ -782,11 +782,11 @@
       </c>
       <c r="H3" s="17" t="inlineStr">
         <is>
-          <t>2,197</t>
+          <t>2,330</t>
         </is>
       </c>
       <c r="I3" s="17">
-        <v>67.1</v>
+        <v>71.4</v>
       </c>
       <c r="J3" s="17" t="inlineStr">
         <is>
@@ -1682,11 +1682,11 @@
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>1,918</t>
+          <t>2,368</t>
         </is>
       </c>
       <c r="I12" s="17">
-        <v>30</v>
+        <v>32.6</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="Q12" s="17" t="inlineStr">
         <is>
-          <t>AL-04: PARAMCD='PFSINV' not derived because the synthetic data has no separate BICR vs Investigator assessment. Affects T-EFF-11. Accepted — not a defect.</t>
+          <t/>
         </is>
       </c>
       <c r="R12" s="17" t="inlineStr">
